--- a/data_extactor/batch_10_fa/batch_0028_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0028_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نوشتن | گوش دادن فعال | درک مطلب | صحبت کردن | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شنیداری | بیان شفاهی | انعطاف‌پذیری بستار | درک نوشتاری | بیان نوشتاری | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | دید دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | تجسم | سرعت بستار | تسهیل عددی | اصالت</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | بیان شفاهی | انعطاف‌پذیری بستار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | بینایی دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | تجسم | سرعت بستار | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | بهداشت و ایمنی سایر کارکنان | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | نزدیکی فیزیکی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | محیط داخلی، بدون کنترل محیطی | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | بازرسان ساخت‌وساز و ساختمان | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و متخصصان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان و محققان آتش‌سوزی | مهندسان پیشگیری و حفاظت از آتش | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | بازرسان و محققان اموال دولتی | کارکنان حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های نظارت هسته‌ای | تکنسین‌های بهداشت و ایمنی شغلی | پزشکان طب پیشگیری | متخصصان مدیریت امنیت | مدیران امنیت | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>بازرسان کشاورزی | بازرسان هوانوردی | بازرسان ساختمان و ساخت‌وساز | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان خط اول آتش‌نشانی و پیشگیری | بازرسان و محققان اموال دولتی | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های نظارت هسته‌ای | تکنسین‌های بهداشت و ایمنی شغلی | پزشکان طب پیشگیری | متخصصان مدیریت امنیت | مدیران امنیتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | صحبت کردن | تفکر انتقادی | نوشتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | دید نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | دید دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | بهداشت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | تکرار تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | فشار زمانی | محیط داخلی، بدون کنترل محیطی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | برخورد با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط بیرونی، در معرض تمام شرایط آب و هوایی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | معلمان آموزش شغلی/فنی، پس از متوسطه | مدیران انطباق | بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت اضطراری | تکنسین‌های فوریت‌های پزشکی | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و متخصصان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مهندسان پیشگیری و حفاظت از آتش | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های نظارت هسته‌ای | متخصصان بهداشت و ایمنی شغلی | پیراپزشکان | پزشکان طب پیشگیری | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>بازرسان کشاورزی | بازرسان هوانوردی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | مدیران انطباق | بازرسان ساختمان و ساخت‌وساز | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مهندسان پیشگیری و حفاظت از آتش‌سوزی | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های نظارت هسته‌ای | متخصصان بهداشت و ایمنی شغلی | پارامدیک‌ها | پزشکان طب پیشگیری | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | تفکر انتقادی | نظارت | نوشتن | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | جامعه‌شناسی و مردم‌شناسی | فلسفه و الهیات | رایانه و الکترونیک | پزشکی و دندانپزشکی | ایمنی و امنیت عمومی</t>
+          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شنیداری | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | دید نزدیک | اصالت | توجه انتخابی | اشتراک زمانی | انعطاف‌پذیری بستار | دید دور</t>
+          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توجه انتخابی | تقسیم توجه | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | تماس با دیگران | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | فشار زمانی | اهمیت تکرار وظایف مشابه | صرف زمان برای نشستن | برخورد با مشتریان خارجی یا عموم مردم | بهداشت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا صحیح بودن | نتایج کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | موقعیت‌های تعارض</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | کارکنان بهداشت جامعه | پزشکان فوریت‌های پزشکی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>پرستاران پیشرفته روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | پزشکان طب اورژانس | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACT Discover | ACT WorkKeys | Adobe ActionScript | Adobe Photoshop | مدیریت پرونده Athena Software Penelope | Blackbaud The Raiser's Edge | Blackboard Wimba | نرم‌افزار Blackboard | Bloomz | Career Cruising | Career Dimensions Focus 2 | Career Zone | برنامه‌های تصمیم‌گیری شغلی | سیستم‌های مدیریت شغلی CMS | CDC WONDER مراکز کنترل و پیشگیری از بیماری | Epi Info مراکز کنترل و پیشگیری از بیماری | نرم‌افزار چت | Coin Educational Products Climb K-5 Online | Coin Educational Products Coin Jr. | College Central Network Career Services Central | Common Curriculum | نرم‌افزار راهنمایی شغلی به کمک رایانه | نظارت زنده به کمک رایانه | برنامه‌های تشخیصی رایانه‌ای | بسته‌های آماری رایانه‌ای | برنامه‌های آزمون رایانه‌ای | نرم‌افزار مشاوره | نرم‌افزار کاربردی پایگاه داده | نرم‌افزار پایگاه داده | EZAnalyze | نرم‌افزار ایمیل | Ext JS | Facebook | FileMaker Pro | Google Classroom | Google Docs | Google Drive | Google Meet | GroupMe | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | Intrado SchoolMessenger | Kuder Navigator | LexisNexis | LinkedIn | LogMeIn GoToMeeting | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Word | Moodle | Naviance Succeed | O*NET OnLine | Oracle PeopleSoft | Oracle Taleo | Orbius | Padlet | Palm Pal Transana | Prezi | نرم‌افزار بهره‌وری | Schoology | Screencastify | SmugMug Flickr | Social Solutions ETO | نرم‌افزار سیستم‌های اطلاعات دانشجویی SIS | نرم‌افزار مرورگر وب | نرم‌افزار طراحی و ویرایش صفحه وب | Yahoo! Email | Zoomerang</t>
+          <t>ACT Discover | ACT WorkKeys | Adobe ActionScript | Adobe Photoshop | مدیریت پرونده Athena Software Penelope | Blackbaud The Raiser's Edge | Blackboard Wimba | نرم‌افزار Blackboard | Bloomz | Career Cruising | Career Dimensions Focus 2 | Career Zone | برنامه‌های تصمیم‌گیری شغلی | سیستم‌های مدیریت شغلی CMS | Centers for Disease Control and Prevention CDC WONDER | Centers for Disease Control and Prevention Epi Info | نرم‌افزار چت | Coin Educational Products Climb K-5 Online | Coin Educational Products Coin Jr. | College Central Network Career Services Central | Common Curriculum | نرم‌افزار راهنمایی شغلی به کمک رایانه | نظارت زنده به کمک رایانه | برنامه‌های تشخیصی رایانه‌ای | بسته‌های آماری رایانه‌ای | برنامه‌های آزمون رایانه‌ای | نرم‌افزار مشاوره | نرم‌افزار کاربردی پایگاه داده | نرم‌افزار پایگاه داده | EZAnalyze | نرم‌افزار ایمیل | Ext JS | Facebook | FileMaker Pro | Google Classroom | Google Docs | Google Drive | Google Meet | GroupMe | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Intrado SchoolMessenger | Kuder Navigator | LexisNexis | LinkedIn | LogMeIn GoToMeeting | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Word | Moodle | Naviance Succeed | O*NET OnLine | Oracle PeopleSoft | Oracle Taleo | Orbius | Padlet | Palm Pal Transana | Prezi | نرم‌افزار بهره‌وری | Schoology | Screencastify | SmugMug Flickr | Social Solutions ETO | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | نرم‌افزار مرورگر وب | نرم‌افزار طراحی و ویرایش صفحه وب | Yahoo! Email | Zoomerang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | دید نزدیک | ترتیب‌دهی اطلاعات | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های تعارض | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های تعارض | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش شغلی/فنی، مدرسه راهنمایی | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مدیران آموزش، مهدکودک تا متوسطه | مدیران آموزش، پس از متوسطه | معلمان آموزش، پس از متوسطه | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش ویژه، مدرسه ابتدایی | معلمان آموزش ویژه، مهدکودک | معلمان آموزش ویژه، مدرسه راهنمایی | معلمان آموزش ویژه، مدرسه متوسطه | متخصصان آموزش و توسعه | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | متخصصان آموزش بهداشت | هماهنگ‌کنندگان آموزشی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | متخصصان آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | نوشتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | اداری | قانون و دولت | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | اداری | قانون و دولت | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | دید نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | تماس با دیگران | تکرار تصمیم‌گیری | فشار زمانی | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | قرار گرفتن در معرض صداها، سطوح سر و صدایی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | فراوانی تصمیم‌گیری | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | درمانگران هنری | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | روان‌شناسان بالینی و مشاوره | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | پزشکان خانواده | مددکاران اجتماعی مراقبت‌های بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | عصب‌روان‌شناسان | کاردرمانگران | دستیاران کاردرمانی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران پیشرفته روانپزشکی | هنردرمانگران | مددکاران اجتماعی کودک، خانواده و مدرسه | عصب‌روان‌شناسان بالینی | روان‌شناسان بالینی و مشاوره | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | پزشکان خانواده | مددکاران اجتماعی مراقبت‌های بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | عصب‌روان‌شناسان | کاردرمانگران | دستیاران کاردرمانی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>سیستم‌های پایگاه داده اطلاعات مشتری | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Google Classroom | سیستم‌های اطلاعات مدیریت MIS | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Netscape Navigator | Oracle PeopleSoft | نرم‌افزار پرونده الکترونیک پزشکی بیمار EMR | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | نرم‌افزار تفسیر آزمون | نرم‌افزار مرورگر وب</t>
+          <t>سیستم‌های پایگاه داده اطلاعات مشتری | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Google Classroom | سیستم‌های اطلاعات مدیریت MIS | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Netscape Navigator | Oracle PeopleSoft | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار زمان‌بندی | نرم‌افزار آماری | نرم‌افزار تفسیر آزمون | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | اداری | مخابرات</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک نوشتاری | بیان نوشتاری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | دید نزدیک | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | تماس با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | کارکنان بهداشت جامعه | پزشکان خانواده | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران پیشرفته روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | پزشکان خانواده | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Acrobat Reader | نرم‌افزار بودجه‌بندی | Chart Links | سیستم‌های پایگاه داده اطلاعات مشتری | نرم‌افزار ورود داده | نرم‌افزار پرونده الکترونیک پزشکی EMR | نرم‌افزار ایمیل | نرم‌افزار رمزگذاری | Fanatic Software Informant | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft ActiveSync | Microsoft Excel | Microsoft Internet Explorer | Microsoft Mobile Explorer MME | Microsoft Office Mobile | Microsoft Office Outlook | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Netscape Navigator | نرم‌افزار زمان‌بندی | SkillTRAN Job Browser Pro | SkillTRAN OASYS | نرم‌افزار تفسیر آزمون | نرم‌افزار محافظت در برابر ویروس | نرم‌افزار مرورگر وب | نرم‌افزار تشخیص کلمه</t>
+          <t>Adobe Acrobat Reader | نرم‌افزار بودجه‌بندی | Chart Links | سیستم‌های پایگاه داده اطلاعات مشتری | نرم‌افزار ورود داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | نرم‌افزار رمزگذاری | Fanatic Software Informant | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft ActiveSync | Microsoft Excel | Microsoft Internet Explorer | Microsoft Mobile Explorer MME | Microsoft Office Mobile | Microsoft Office Outlook | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Netscape Navigator | نرم‌افزار زمان‌بندی | SkillTRAN Job Browser Pro | SkillTRAN OASYS | نرم‌افزار تفسیر آزمون | نرم‌افزار محافظت در برابر ویروس | نرم‌افزار مرورگر وب | نرم‌افزار تشخیص کلمه</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | نظارت | درک مطلب | نوشتن | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | اداری | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی | پرسنل و منابع انسانی | مدیریت و اداره | ایمنی و امنیت عمومی | قانون و دولت</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | اداری | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی | مدیریت و اداره | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شنیداری | بیان شفاهی | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تکرار تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | کارکنان بهداشت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک پزشکی EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office | Microsoft PowerPoint</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office | Microsoft PowerPoint</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | مددکاران اجتماعی، سایر | متخصصان آموزش بهداشت | افسران آزادی مشروط و متخصصان درمان اصلاحی | دستیاران خدمات اجتماعی و انسانی | کارکنان بهداشت جامعه | متخصصان خدمات اجتماعی و جامعه، سایر | روحانیون | روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | معلمان مددکاری اجتماعی، پس از متوسطه | مدیران خدمات اجتماعی و جامعه | درمانگران تفریحی</t>
+          <t>مشاوران سوءمصرف مواد و اختلالات رفتاری | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی مراقبت‌های بهداشتی | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مددکاران اجتماعی، سایر | متخصصان آموزش بهداشت | افسران مشروط و متخصصان درمان اصلاحی | دستیاران خدمات اجتماعی و انسانی | مددکاران سلامت جامعه | متخصصان خدمات اجتماعی و جامعه، سایر | روحانیون | روان‌شناسان بالینی و مشاوره | روان‌شناسان مدرسه | مدرسان مددکاری اجتماعی، آموزش عالی | مدیران خدمات اجتماعی و جامعه | درمانگران تفریحی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EasyCBM | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک پزشکی بیمار EMR | نرم‌افزار سیستم‌های اطلاعات دانشجویی SIS | نرم‌افزار مرورگر وب</t>
+          <t>EasyCBM | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | تفکر انتقادی | درک مطلب | نظارت | نوشتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | قانون و دولت</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | حساسیت به مسئله | درک نوشتاری | بیان نوشتاری | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | دید نزدیک | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامد خطا | صرف زمان برای نشستن</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاوره | کارکنان بهداشت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | نمایندگان بیمار | دستیاران مراقبت شخصی | افسران آزادی مشروط و متخصصان درمان اصلاحی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | افسران مشروط و متخصصان درمان اصلاحی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مشاوران توانبخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe PageMaker | سیستم‌های اطلاعات بالینی خودکار | نرم‌افزار تقویم | Command Systems ComServe | مجموعه نرم‌افزاری Corel WordPerfect Office | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Google Meet | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | نرم‌افزار ارائه اطلاعات | Intrado SchoolMessenger | James Frazier Associates DataStart | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار سوابق پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Publisher | Microsoft Teams | Microsoft Word | نرم‌افزار پرونده الکترونیک پزشکی بیمار EMR | نرم‌افزار پایگاه داده رابطه‌ای | Social Solutions ETO | Social Work Software ClientTouch | نرم‌افزار مرورگر وب | نرم‌افزار طراحی و ویرایش صفحه وب | Zoom</t>
+          <t>Adobe PageMaker | سیستم‌های اطلاعات بالینی خودکار | نرم‌افزار تقویم | Command Systems ComServe | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Google Meet | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار ارائه اطلاعات | Intrado SchoolMessenger | James Frazier Associates DataStart | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار سوابق پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Publisher | Microsoft Teams | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار پایگاه داده رابطه‌ای | Social Solutions ETO | Social Work Software ClientTouch | نرم‌افزار مرورگر وب | نرم‌افزار طراحی و ویرایش صفحه وب | Zoom</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | فلسفه و الهیات | اداری</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | فلسفه و الهیات | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک شنیداری | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | دید نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض بیماری یا عفونت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | موقعیت‌های تعارض | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | موقعیت‌های تعارض | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تمرین پیشرفته | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | کارکنان بهداشت جامعه | پزشکان خانواده | متخصصان آموزش بهداشت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | دستیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>پرستاران پیشرفته روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | مددکاران سلامت جامعه | پزشکان خانواده | متخصصان آموزش بهداشت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0028_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0028_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | شیمی | آموزش و پرورش | ریاضیات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | زیست‌شناسی | حقوق و امور دولتی | ایمنی و امنیت عمومی | مدیریت و امور اداری | ساختمان و سازه | مکانیک | رایانه و الکترونیک | امور دفتری و اداری | تولید و فراوری | فیزیک | طراحی</t>
+          <t>زبان انگلیسی | شیمی | آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | زیست‌شناسی | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و اداره | ساختمان و ساخت‌وساز | مکانیک | رایانه و الکترونیک | اداری | تولید و فرآوری | فیزیک | طراحی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | بیان شفاهی | انعطاف‌پذیری در نتیجه‌گیری | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | طبقه‌بندی منعطف | روانی کلام و سیالی ایده‌ها | دید دور | دقت انتخابی | سرعت ادراک | استدلال ریاضی | تجسم فضایی | سرعت در نتیجه‌گیری | کار با اعداد | اصالت و ابتکار عمل</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | بیان شفاهی | انعطاف‌پذیری بستار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | بینایی دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | تجسم | سرعت بستار | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | بازرسان ساختمان و سازه | بازرسان انطباق با مقررات زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان و تکنسین‌های علوم محیطی و حفاظت، شامل بهداشت | دانشمندان و متخصصان علوم محیطی، شامل بهداشت | بازرسان و کارشناسان بررسی حریق | مهندسان پیشگیری و حفاظت در برابر حریق | سرپرستان رده‌اول آتش‌نشانان و نیروهای پیشگیری از حریق | بازرسان و کارشناسان اموال دولتی | کارگران جمع‌آوری و پاک‌سازی پسماندهای خطرناک | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معادن | تکنسین‌های پایش پرتوی و هسته‌ای | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | پزشکان طب کار و پزشکی پیشگیری | کارشناسان مدیریت انتظامات و امنیت | مدیران حراست و انتظامات | بازرسان وسایل، تجهیزات و سامانه‌های حمل‌ونقل، به‌جز هوانوردی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | بازرسان هوانوردی و فرودگاهی | بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | بازرسان و ممیزان اموال دولتی | کارگران امحا و پاک‌سازی مواد خطرناک | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های پایش و حفاظت پرتوی | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان پزشکی اجتماعی و طب پیشگیری | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | حقوق و امور دولتی | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | مکانیک | رایانه و الکترونیک | ساختمان و سازه | شیمی | تولید و فراوری | روان‌شناسی | فیزیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | مهندسی و فناوری | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | مکانیک | رایانه و الکترونیک | ساختمان و ساخت‌وساز | شیمی | تولید و فرآوری | روان‌شناسی | فیزیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | دید نزدیک | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید دور | طبقه‌بندی منعطف | انعطاف‌پذیری در نتیجه‌گیری | دقت انتخابی | سرعت ادراک | اصالت و ابتکار عمل | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | مدرسان آموزش فنی و حرفه‌ای پس از دیپلم | مدیران انطباق با مقررات | بازرسان ساختمان و سازه | مدیران مدیریت بحران | کاردان‌ها و تکنسین‌های فوریت‌های پزشکی | بازرسان انطباق با مقررات زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان و تکنسین‌های علوم محیطی و حفاظت، شامل بهداشت | دانشمندان و متخصصان علوم محیطی، شامل بهداشت | مهندسان پیشگیری و حفاظت در برابر حریق | بازرسان و کارشناسان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معادن | تکنسین‌های پایش پرتوی و هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان فوریت‌های پزشکی (پارامدیک) | پزشکان طب کار و پزشکی پیشگیری | بازرسان وسایل، تجهیزات و سامانه‌های حمل‌ونقل، به‌جز هوانوردی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | بازرسان هوانوردی و فرودگاهی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مدیران تطبیق و نظارت مقرراتی | بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان پیشگیری و حفاظت از حریق | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های پایش و حفاظت پرتوی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | متخصصان پزشکی اجتماعی و طب پیشگیری | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور دفتری و اداری | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | فلسفه و الهیات | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
+          <t>درمان و مشاوره | روان‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | طبقه‌بندی منعطف | دید نزدیک | اصالت و ابتکار عمل | دقت انتخابی | تقسیم توجه | انعطاف‌پذیری در نتیجه‌گیری | دید دور</t>
+          <t>بیان شفاهی | حساسیت به مسئله | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توجه انتخابی | تقسیم توجه | انعطاف‌پذیری بستار | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | مراقبان و رابطان سلامت جامعه | پزشکان طب اورژانس | کارشناسان آموزش و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌کاردرمانگران | کاردان‌های کاردرمانی | کمک‌فیزیوتراپ‌ها | بهیاران و کمک‌های روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | دستیاران و کاردان‌های خدمات اجتماعی و انسانی</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | پزشکان طب اورژانس | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | روان‌شناسی | امور دفتری و اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | دید نزدیک | مرتب‌سازی اطلاعات | اصالت و ابتکار عمل | دقت انتخابی | طبقه‌بندی منعطف</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی و آموزش بزرگسالان و آموزش زبان انگلیسی | دبیران آموزش فنی و حرفه‌ای دوره متوسطه اول | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | مدیران اداری و آموزشی مدارس | مدیران آموزش عالی | استادان علوم تربیتی و آموزش در دانشگاه | کارشناسان آموزش و ارتقای سلامت | کارشناسان برنامه‌ریزی درسی و آموزشی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | معلمان آموزش استثنایی دوره ابتدایی | مربیان آموزش استثنایی دوره پیش‌دبستانی | معلمان آموزش استثنایی دوره متوسطه اول | معلمان آموزش استثنایی دوره متوسطه دوم | کارشناسان آموزش و توانمندسازی منابع انسانی | مدرسان خصوصی و معلمان تقویتی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | روان‌شناسان مدارس | دستیاران خدمات اجتماعی و انسانی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کارشناسان آموزش و توسعه منابع انسانی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | امور دفتری و اداری | حقوق و امور دولتی | فلسفه و الهیات</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | اداری | قانون و دولت | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | طبقه‌بندی منعطف | مرتب‌سازی اطلاعات | روانی کلام و سیالی ایده‌ها | اصالت و ابتکار عمل | دید نزدیک | دقت انتخابی | انعطاف‌پذیری در نتیجه‌گیری | سرعت در نتیجه‌گیری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | اصالت | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | هنردرمانگران | مددکاران اجتماعی کودک، خانواده و مدرسه | نوروسایکولوژیست‌های بالینی | روان‌شناسان بالینی و مشاور | مشاوران تحصیلی، شغلی و هدایت استعدادها | پزشکان عمومی و خانواده | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | کاردرمانگران | کاردان‌های کاردرمانی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدرسه | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>پرستاران تخصصی روانپزشکی | هنر‌درمانگران | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان عصب‌روان‌شناسی بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | مشاوران تحصیلی، شغلی و هدایت استعدادها | پزشکان عمومی و خانواده | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | متخصصان عصب‌روان‌شناسی | کاردرمانگران | کاردان‌های کاردرمانی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدارس | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | امور دفتری و اداری | مخابرات و ارتباطات</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | طبقه‌بندی منعطف | روانی کلام و سیالی ایده‌ها | اصالت و ابتکار عمل | دقت انتخابی | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان ارشد پرستاری بالینی | روان‌شناسان بالینی و مشاور | مراقبان و رابطان سلامت جامعه | پزشکان عمومی و خانواده | کارشناسان آموزش و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌کاردرمانگران | کاردان‌های کاردرمانی | بهیاران و کمک‌های روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | پزشکان عمومی و خانواده | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | امور دفتری و اداری | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی | امور کارکنان و منابع انسانی | مدیریت و امور اداری | ایمنی و امنیت عمومی | حقوق و امور دولتی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | اداری | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی | پرسنل و منابع انسانی | مدیریت و اداره | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | دید نزدیک | طبقه‌بندی منعطف | مرتب‌سازی اطلاعات | اصالت و ابتکار عمل | روانی کلام و سیالی ایده‌ها</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاور | مراقبان و رابطان سلامت جامعه | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران کم‌بینایی، کارشناسان جهت‌یابی و تحرک، و توانبخش‌های بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌کاردرمانگران | کاردان‌های کاردرمانی | کمک‌فیزیوتراپ‌ها | بهیاران و کمک‌های روان‌پزشکی | تکنسین‌های روان‌پزشکی | کارشناسان تفریح‌درمانی | مدیران خدمات اجتماعی و خدمات جامعه‌محور | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی | مدیریت و امور اداری</t>
+          <t>درمان و مشاوره | روان‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | طبقه‌بندی منعطف | روانی کلام و سیالی ایده‌ها | اصالت و ابتکار عمل | دقت انتخابی | تقسیم توجه | تجسم فضایی | به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مشاوران اعتیاد و اختلالات رفتاری | مشاوران تحصیلی، شغلی و هدایت استعدادها | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | سایر مددکاران اجتماعی | کارشناسان آموزش و ارتقای سلامت | افسران مراقبت و کارشناسان بازپروری و اصلاح و تربیت | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مراقبان و رابطان سلامت جامعه | سایر متخصصان خدمات اجتماعی و خدمات جامعه‌محور | روحانیون و مبلغان مذهبی | روان‌شناسان بالینی و مشاور | روان‌شناسان مدرسه | مدرسان مددکاری اجتماعی در دانشگاه | مدیران خدمات اجتماعی و خدمات جامعه‌محور | کارشناسان تفریح‌درمانی</t>
+          <t>مشاوران اعتیاد و اختلالات رفتاری | مشاوران تحصیلی، شغلی و هدایت استعدادها | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مشاوران توانبخشی | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مددکاران اجتماعی، سایر تخصص‌ها | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران قضایی و متخصصان اصلاح و تربیت | دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | سایر متخصصان خدمات اجتماعی و عمومی | روحانیون و مبلغان مذهبی | روان‌شناسان بالینی و مشاوران سلامت روان | روان‌شناسان مدارس | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | مدیران خدمات اجتماعی و خدمات مردمی | کارشناسان تفریح‌درمانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | امور دفتری و اداری | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | اداری | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | مرتب‌سازی اطلاعات | دید نزدیک | اصالت و ابتکار عمل | روانی کلام و سیالی ایده‌ها | طبقه‌بندی منعطف | دقت انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>روان‌شناسان بالینی و مشاور | مراقبان و رابطان سلامت جامعه | مشاوران تحصیلی، شغلی و هدایت استعدادها | مصاحبه‌گران تعیین واجدین شرایط در برنامه‌های دولتی | کارشناسان آموزش و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | نمایندگان حقوق بیمار | نیروهای مراقبت و همیار فردی | افسران مراقبت و کارشناسان بازپروری و اصلاح و تربیت | بهیاران و کمک‌های روان‌پزشکی | تکنسین‌های روان‌پزشکی | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدرسه | مدیران خدمات اجتماعی و خدمات جامعه‌محور | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | مددکاران قضایی و متخصصان اصلاح و تربیت | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | روان‌شناسان مدارس | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | فلسفه و الهیات | امور دفتری و اداری</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | فلسفه و الهیات | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | روانی کلام و سیالی ایده‌ها | مرتب‌سازی اطلاعات | دید نزدیک | دقت انتخابی | طبقه‌بندی منعطف | اصالت و ابتکار عمل</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران تخصصی روان‌پزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان ارشد پرستاری بالینی | روان‌شناسان بالینی و مشاور | مراقبان و رابطان سلامت جامعه | پزشکان عمومی و خانواده | کارشناسان آموزش و ارتقای سلامت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران دوره‌دیده مراقبت‌های ویژه (NP) | کاردرمانگران | کاردان‌های کاردرمانی | بهیاران و کمک‌های روان‌پزشکی | تکنسین‌های روان‌پزشکی | روان‌پزشکان | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات جامعه‌محور | دستیاران و کاردان‌های خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
+          <t>پرستاران تخصصی روانپزشکی | مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | رابطان سلامت و بهورزان | پزشکان عمومی و خانواده | کارشناسان آموزش بهداشت و ارتقای سلامت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | کاردرمانگران | کاردان‌های کاردرمانی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
